--- a/excel-files/QUEZON CITY/BAGONG PAG-ASA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/BAGONG PAG-ASA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10320"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC554E4D-6E5C-4D5D-B58B-564F6F369FCC}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D31FFBCE-5248-9845-BEE4-501A83D8A60E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -314,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,6 +736,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,1115 +754,11 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="63">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color rgb="FF000000"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFCAEDFB"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2934,13 +1836,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2980,6 +1875,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3005,6 +1907,1104 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color rgb="FF000000"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFCAEDFB"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3019,7 +3019,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3036,54 +3036,54 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="23">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="19">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="48">
+    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="18">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="47">
+    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="17">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="11">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="37">
+    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="7">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="36">
+    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="6">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="35">
+    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="5">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="33"/>
-    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="32"/>
-    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="31">
+    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="1">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30">
+    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="0">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3092,54 +3092,54 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="56">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="52">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="18">
+    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="51">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="17">
+    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="50">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="46"/>
+    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="45"/>
+    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="44">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="7">
+    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="42"/>
+    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="40">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="6">
+    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="39">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="5">
+    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="38">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="4"/>
-    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="3"/>
-    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="2"/>
-    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="1">
+    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="35"/>
+    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="34">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="0">
+    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="33">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3465,17 +3465,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3501,14 +3501,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1">
+        <v>207</v>
+      </c>
       <c r="D2" s="1">
         <v>284</v>
       </c>
@@ -3520,17 +3522,19 @@
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1">
+        <v>207</v>
+      </c>
       <c r="D3" s="1">
         <v>284</v>
       </c>
@@ -3542,17 +3546,19 @@
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>284</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1">
+        <v>207</v>
+      </c>
       <c r="D4" s="1">
         <v>284</v>
       </c>
@@ -3564,17 +3570,19 @@
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>284</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>207</v>
+      </c>
       <c r="D5" s="1">
         <v>284</v>
       </c>
@@ -3586,55 +3594,59 @@
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>207</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>268</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3654,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3674,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3694,7 +3706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3714,32 +3726,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>281</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3759,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3779,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3799,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3819,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3839,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3849,14 +3863,16 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>244</v>
+      </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
@@ -3864,14 +3880,14 @@
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3893,7 +3909,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.5">
+    <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3915,7 +3931,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3937,7 +3953,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3959,7 +3975,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -3981,7 +3997,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4003,7 +4019,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4023,7 +4039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4043,7 +4059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4053,27 +4069,29 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <v>252</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4093,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4113,7 +4131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4133,7 +4151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4155,7 +4173,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4175,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4195,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4215,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4235,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4245,27 +4263,29 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>225</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4285,7 +4305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4305,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4325,7 +4345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4345,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4365,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4385,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4405,7 +4425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4425,7 +4445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4435,7 +4455,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4455,7 +4475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4475,7 +4495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4495,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4515,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4535,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4555,7 +4575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4575,7 +4595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4595,7 +4615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4615,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4625,7 +4645,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4645,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4665,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4685,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4705,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4725,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4745,7 +4765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4765,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4785,7 +4805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4805,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4815,7 +4835,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4835,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4855,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4875,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -4895,7 +4915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -4915,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4935,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -4955,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -4975,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -4995,7 +5015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5005,7 +5025,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5025,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5045,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5065,7 +5085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5085,7 +5105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5105,7 +5125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5125,7 +5145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5145,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5165,7 +5185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5185,7 +5205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5195,7 +5215,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>23</v>
       </c>
@@ -5215,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -5235,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>23</v>
       </c>
@@ -5255,7 +5275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>23</v>
       </c>
@@ -5275,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>23</v>
       </c>
@@ -5295,7 +5315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>23</v>
       </c>
@@ -5315,7 +5335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -5335,7 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>23</v>
       </c>
@@ -5362,8 +5382,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5378,70 +5398,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-    </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+    </row>
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5478,10 +5498,10 @@
       <c r="L2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>46</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5514,17 +5534,17 @@
       <c r="X2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>58</v>
       </c>
       <c r="AA2" s="26" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>60</v>
       </c>
@@ -5591,7 +5611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5603,7 +5623,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5672,7 +5692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5741,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5810,7 +5830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5879,7 +5899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5948,7 +5968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6017,7 +6037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6086,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6155,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6168,7 +6188,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6237,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6306,7 +6326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6375,7 +6395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6444,7 +6464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6513,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6582,7 +6602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6651,7 +6671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6720,7 +6740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6734,7 +6754,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6803,7 +6823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6872,7 +6892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6941,7 +6961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7010,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7079,7 +7099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7148,7 +7168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7217,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7286,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7355,7 +7375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7369,7 +7389,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7438,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7507,7 +7527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7576,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7645,7 +7665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7714,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7783,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7852,7 +7872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7921,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -7990,7 +8010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8004,7 +8024,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8073,7 +8093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8142,7 +8162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8211,7 +8231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8280,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8349,7 +8369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8418,7 +8438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8487,7 +8507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8556,7 +8576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8625,7 +8645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8639,7 +8659,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8708,7 +8728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8777,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8846,7 +8866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8915,7 +8935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -8984,7 +9004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9053,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9122,7 +9142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9191,7 +9211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9260,7 +9280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9274,7 +9294,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9343,7 +9363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9412,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9481,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9550,7 +9570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9619,7 +9639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9688,7 +9708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9757,7 +9777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9826,7 +9846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9895,7 +9915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9909,7 +9929,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9978,7 +9998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10047,7 +10067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10116,7 +10136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10185,7 +10205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10254,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10323,7 +10343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10392,7 +10412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10461,7 +10481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10530,7 +10550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10544,7 +10564,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10613,7 +10633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10682,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10751,7 +10771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10820,7 +10840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10889,7 +10909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10958,7 +10978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11027,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11096,7 +11116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11165,7 +11185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11179,7 +11199,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11248,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11317,7 +11337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11386,7 +11406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11455,7 +11475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11524,7 +11544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11593,7 +11613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11662,7 +11682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11731,7 +11751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11800,7 +11820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11814,7 +11834,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11883,7 +11903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -11952,7 +11972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12021,7 +12041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12090,7 +12110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12159,7 +12179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12228,7 +12248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12297,7 +12317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12366,7 +12386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12377,7 +12397,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12439,7 +12459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12501,7 +12521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12563,7 +12583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12625,7 +12645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12687,7 +12707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12749,7 +12769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12811,7 +12831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12873,7 +12893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -12935,7 +12955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -12997,7 +13017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13059,7 +13079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13121,7 +13141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13183,7 +13203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13245,7 +13265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13307,7 +13327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13364,186 +13384,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13563,8 +13403,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13582,70 +13422,70 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-    </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+    </row>
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13682,10 +13522,10 @@
       <c r="L2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>72</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13718,17 +13558,17 @@
       <c r="X2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AA2" s="26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13797,7 +13637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13866,7 +13706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13935,7 +13775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14004,7 +13844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14073,7 +13913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14142,7 +13982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14211,7 +14051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14280,8 +14120,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14350,7 +14190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14419,7 +14259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14488,7 +14328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14557,7 +14397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14626,7 +14466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14695,7 +14535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14764,7 +14604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14833,8 +14673,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14903,7 +14743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14972,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15041,7 +14881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15110,7 +14950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15179,7 +15019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15248,7 +15088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15317,7 +15157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15386,7 +15226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15455,8 +15295,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15525,7 +15365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15594,7 +15434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15663,7 +15503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15732,7 +15572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15801,7 +15641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15870,7 +15710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15939,7 +15779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16008,7 +15848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16077,7 +15917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16146,7 +15986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16215,8 +16055,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16285,7 +16125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16354,7 +16194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16423,7 +16263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16492,7 +16332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16561,7 +16401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16630,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16699,7 +16539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16768,7 +16608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16837,7 +16677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16906,7 +16746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -16975,8 +16815,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17045,7 +16885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17114,7 +16954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17183,7 +17023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17252,7 +17092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17321,7 +17161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17390,7 +17230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17459,7 +17299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17528,7 +17368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17597,7 +17437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17666,7 +17506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17735,8 +17575,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17805,7 +17645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17874,7 +17714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17943,7 +17783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18012,7 +17852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18081,7 +17921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18150,7 +17990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18219,7 +18059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18288,7 +18128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18357,7 +18197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18426,7 +18266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18495,8 +18335,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18565,7 +18405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18634,7 +18474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18703,7 +18543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18772,7 +18612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18841,7 +18681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18910,7 +18750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -18979,7 +18819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19048,7 +18888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19117,7 +18957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19186,7 +19026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19255,8 +19095,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19325,7 +19165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19394,7 +19234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19463,7 +19303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19532,7 +19372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19601,7 +19441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19670,7 +19510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19739,7 +19579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19808,7 +19648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19877,7 +19717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -19946,7 +19786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20015,8 +19855,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20085,7 +19925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20154,7 +19994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20223,7 +20063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20292,7 +20132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20361,7 +20201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20430,7 +20270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20499,7 +20339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20568,7 +20408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20637,7 +20477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20706,7 +20546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20775,8 +20615,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20845,7 +20685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20914,7 +20754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -20983,7 +20823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21052,7 +20892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21121,7 +20961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21190,7 +21030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21259,7 +21099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21328,8 +21168,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21359,7 +21199,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21389,7 +21229,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21419,7 +21259,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21449,7 +21289,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21479,7 +21319,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21509,7 +21349,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21539,7 +21379,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21569,7 +21409,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21599,7 +21439,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21629,7 +21469,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21659,7 +21499,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21689,7 +21529,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21719,7 +21559,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21749,7 +21589,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21779,7 +21619,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -21809,7 +21649,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -21839,186 +21679,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22036,8 +21696,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F91:F113 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L91:L113 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R91:R113 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X91:X113 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{50476973-B142-4F71-9078-8C0E9A418AF0}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
